--- a/sample_data/C_legacy_pos/i-3-STOCK COST.xlsx
+++ b/sample_data/C_legacy_pos/i-3-STOCK COST.xlsx
@@ -476,7 +476,7 @@
         <v>655.92</v>
       </c>
       <c r="F3" t="n">
-        <v>800.28</v>
+        <v>603.36</v>
       </c>
     </row>
     <row r="4">
@@ -491,16 +491,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>32.33</v>
+        <v>34.64</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>831.36</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1014.24</v>
       </c>
     </row>
     <row r="5">
@@ -515,16 +515,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>41.71</v>
+        <v>39.72</v>
       </c>
       <c r="E5" t="n">
-        <v>3420.22</v>
+        <v>357.48</v>
       </c>
       <c r="F5" t="n">
-        <v>4104.1</v>
+        <v>428.94</v>
       </c>
     </row>
     <row r="6">
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>52.51</v>
+        <v>52.32</v>
       </c>
       <c r="E6" t="n">
-        <v>4148.29</v>
+        <v>1098.72</v>
       </c>
       <c r="F6" t="n">
-        <v>4894.84</v>
+        <v>1296.54</v>
       </c>
     </row>
     <row r="7">
@@ -563,16 +563,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>452</v>
+        <v>395</v>
       </c>
       <c r="D7" t="n">
-        <v>27.14</v>
+        <v>26.8</v>
       </c>
       <c r="E7" t="n">
-        <v>12267.28</v>
+        <v>10586</v>
       </c>
       <c r="F7" t="n">
-        <v>15331.84</v>
+        <v>13232.5</v>
       </c>
     </row>
     <row r="8">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D8" t="n">
-        <v>32.79</v>
+        <v>33.39</v>
       </c>
       <c r="E8" t="n">
-        <v>754.17</v>
+        <v>1101.87</v>
       </c>
       <c r="F8" t="n">
-        <v>693.91</v>
+        <v>1333.2</v>
       </c>
     </row>
     <row r="9">
@@ -611,16 +611,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
-        <v>123.21</v>
+        <v>117.57</v>
       </c>
       <c r="E9" t="n">
-        <v>985.6799999999999</v>
+        <v>3174.39</v>
       </c>
       <c r="F9" t="n">
-        <v>1133.52</v>
+        <v>3650.67</v>
       </c>
     </row>
     <row r="10">
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>89.55</v>
+        <v>88.52</v>
       </c>
       <c r="E10" t="n">
-        <v>5014.8</v>
+        <v>1681.88</v>
       </c>
       <c r="F10" t="n">
-        <v>5766.88</v>
+        <v>1934.2</v>
       </c>
     </row>
     <row r="11">
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>109.12</v>
+        <v>104.32</v>
       </c>
       <c r="E11" t="n">
-        <v>12985.28</v>
+        <v>208.64</v>
       </c>
       <c r="F11" t="n">
-        <v>15192.73</v>
+        <v>244.1</v>
       </c>
     </row>
     <row r="12">
@@ -683,16 +683,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>22.84</v>
+        <v>24.86</v>
       </c>
       <c r="E12" t="n">
-        <v>1644.48</v>
+        <v>3306.38</v>
       </c>
       <c r="F12" t="n">
-        <v>2055.6</v>
+        <v>4132.31</v>
       </c>
     </row>
     <row r="13">
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>75.23</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1128.45</v>
+        <v>828.1900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1309.05</v>
+        <v>960.74</v>
       </c>
     </row>
     <row r="14">
@@ -731,16 +731,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>161.13</v>
+        <v>171.16</v>
       </c>
       <c r="E14" t="n">
-        <v>5478.42</v>
+        <v>1198.12</v>
       </c>
       <c r="F14" t="n">
-        <v>6245.46</v>
+        <v>1365.84</v>
       </c>
     </row>
     <row r="15">
@@ -755,16 +755,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>87.51000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="E15" t="n">
-        <v>7963.41</v>
+        <v>1010.24</v>
       </c>
       <c r="F15" t="n">
-        <v>9237.41</v>
+        <v>1171.83</v>
       </c>
     </row>
     <row r="16">
@@ -782,13 +782,13 @@
         <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>66.42</v>
+        <v>65.7</v>
       </c>
       <c r="E16" t="n">
-        <v>1261.98</v>
+        <v>1248.3</v>
       </c>
       <c r="F16" t="n">
-        <v>1489.22</v>
+        <v>1473.07</v>
       </c>
     </row>
     <row r="17">
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>76.75</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>3760.75</v>
+        <v>769.3</v>
       </c>
       <c r="F17" t="n">
-        <v>4437.44</v>
+        <v>907.8</v>
       </c>
     </row>
     <row r="18">
@@ -827,16 +827,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>95.78</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>2202.94</v>
+        <v>1745.28</v>
       </c>
       <c r="F18" t="n">
-        <v>2555.3</v>
+        <v>2024.46</v>
       </c>
     </row>
     <row r="19">
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="D19" t="n">
-        <v>176.12</v>
+        <v>187.29</v>
       </c>
       <c r="E19" t="n">
-        <v>5459.72</v>
+        <v>19103.58</v>
       </c>
       <c r="F19" t="n">
-        <v>6169.62</v>
+        <v>21587.28</v>
       </c>
     </row>
     <row r="20">
@@ -875,16 +875,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
-        <v>202.29</v>
+        <v>217.19</v>
       </c>
       <c r="E20" t="n">
-        <v>14564.88</v>
+        <v>12814.21</v>
       </c>
       <c r="F20" t="n">
-        <v>16312.32</v>
+        <v>14351.75</v>
       </c>
     </row>
     <row r="21">
@@ -899,16 +899,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="D21" t="n">
-        <v>9.09</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>1081.71</v>
+        <v>499.96</v>
       </c>
       <c r="F21" t="n">
-        <v>1406.58</v>
+        <v>650.1799999999999</v>
       </c>
     </row>
     <row r="22">
@@ -923,16 +923,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>235.77</v>
+        <v>241.56</v>
       </c>
       <c r="E22" t="n">
-        <v>2357.7</v>
+        <v>5314.32</v>
       </c>
       <c r="F22" t="n">
-        <v>2617</v>
+        <v>5898.86</v>
       </c>
     </row>
     <row r="23">
@@ -947,16 +947,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>46.79</v>
+        <v>44.08</v>
       </c>
       <c r="E23" t="n">
-        <v>140.37</v>
+        <v>1586.88</v>
       </c>
       <c r="F23" t="n">
-        <v>168.45</v>
+        <v>1904.4</v>
       </c>
     </row>
     <row r="24">
@@ -971,16 +971,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>56.58</v>
+        <v>59.59</v>
       </c>
       <c r="E24" t="n">
-        <v>5997.48</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>7136.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -998,7 +998,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>69.84999999999999</v>
+        <v>72.56</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D26" t="n">
-        <v>385.01</v>
+        <v>397.77</v>
       </c>
       <c r="E26" t="n">
-        <v>6930.18</v>
+        <v>35401.53</v>
       </c>
       <c r="F26" t="n">
-        <v>7623.18</v>
+        <v>38941.95</v>
       </c>
     </row>
     <row r="27">
@@ -1043,16 +1043,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="D27" t="n">
-        <v>313.89</v>
+        <v>306.03</v>
       </c>
       <c r="E27" t="n">
-        <v>28250.1</v>
+        <v>5814.57</v>
       </c>
       <c r="F27" t="n">
-        <v>31357.8</v>
+        <v>6454.11</v>
       </c>
     </row>
     <row r="28">
@@ -1067,16 +1067,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D28" t="n">
-        <v>513.1900000000001</v>
+        <v>513.4</v>
       </c>
       <c r="E28" t="n">
-        <v>11803.37</v>
+        <v>19509.2</v>
       </c>
       <c r="F28" t="n">
-        <v>12747.75</v>
+        <v>21069.86</v>
       </c>
     </row>
     <row r="29">
@@ -1091,16 +1091,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>161.07</v>
+        <v>159.46</v>
       </c>
       <c r="E29" t="n">
-        <v>2577.12</v>
+        <v>5740.56</v>
       </c>
       <c r="F29" t="n">
-        <v>2834.88</v>
+        <v>6314.76</v>
       </c>
     </row>
     <row r="30">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>131.97</v>
+        <v>143.73</v>
       </c>
       <c r="E30" t="n">
-        <v>3299.25</v>
+        <v>1724.76</v>
       </c>
       <c r="F30" t="n">
-        <v>3827.25</v>
+        <v>2000.76</v>
       </c>
     </row>
     <row r="31">
@@ -1139,16 +1139,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="D31" t="n">
-        <v>111.4</v>
+        <v>108.36</v>
       </c>
       <c r="E31" t="n">
-        <v>6015.6</v>
+        <v>2709</v>
       </c>
       <c r="F31" t="n">
-        <v>7038.36</v>
+        <v>3169.5</v>
       </c>
     </row>
     <row r="32">
@@ -1163,16 +1163,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D32" t="n">
-        <v>30.46</v>
+        <v>31.89</v>
       </c>
       <c r="E32" t="n">
-        <v>791.96</v>
+        <v>446.46</v>
       </c>
       <c r="F32" t="n">
-        <v>982.02</v>
+        <v>553.5599999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1187,16 +1187,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>482</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>37.12</v>
+        <v>37.63</v>
       </c>
       <c r="E33" t="n">
-        <v>17891.84</v>
+        <v>564.45</v>
       </c>
       <c r="F33" t="n">
-        <v>21829.78</v>
+        <v>688.65</v>
       </c>
     </row>
     <row r="34">
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>73.91</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>469</v>
+        <v>85</v>
       </c>
       <c r="D35" t="n">
-        <v>37.62</v>
+        <v>37.32</v>
       </c>
       <c r="E35" t="n">
-        <v>17643.78</v>
+        <v>3172.2</v>
       </c>
       <c r="F35" t="n">
-        <v>21527.1</v>
+        <v>3870.05</v>
       </c>
     </row>
     <row r="36">
@@ -1259,16 +1259,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="D36" t="n">
-        <v>41.81</v>
+        <v>43.56</v>
       </c>
       <c r="E36" t="n">
-        <v>7943.9</v>
+        <v>609.84</v>
       </c>
       <c r="F36" t="n">
-        <v>9612.1</v>
+        <v>737.9400000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1283,16 +1283,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D37" t="n">
-        <v>47.76</v>
+        <v>50.75</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1827</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2210.76</v>
       </c>
     </row>
     <row r="38">
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="D38" t="n">
-        <v>59.86</v>
+        <v>57.66</v>
       </c>
       <c r="E38" t="n">
-        <v>5926.14</v>
+        <v>1845.12</v>
       </c>
       <c r="F38" t="n">
-        <v>7111.17</v>
+        <v>2214.08</v>
       </c>
     </row>
     <row r="39">
@@ -1331,16 +1331,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D39" t="n">
-        <v>84.18000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="E39" t="n">
-        <v>1515.24</v>
+        <v>3702.16</v>
       </c>
       <c r="F39" t="n">
-        <v>1787.94</v>
+        <v>4368.76</v>
       </c>
     </row>
     <row r="40">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D40" t="n">
-        <v>62.42</v>
+        <v>59.89</v>
       </c>
       <c r="E40" t="n">
-        <v>1310.82</v>
+        <v>1976.37</v>
       </c>
       <c r="F40" t="n">
-        <v>1559.88</v>
+        <v>2351.91</v>
       </c>
     </row>
     <row r="41">
@@ -1379,16 +1379,16 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>45.03</v>
+        <v>48.6</v>
       </c>
       <c r="E41" t="n">
-        <v>2116.41</v>
+        <v>291.6</v>
       </c>
       <c r="F41" t="n">
-        <v>2539.88</v>
+        <v>349.92</v>
       </c>
     </row>
     <row r="42">
@@ -1403,16 +1403,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="D42" t="n">
-        <v>433.86</v>
+        <v>423.78</v>
       </c>
       <c r="E42" t="n">
-        <v>35142.66</v>
+        <v>8051.82</v>
       </c>
       <c r="F42" t="n">
-        <v>38305.71</v>
+        <v>8776.48</v>
       </c>
     </row>
     <row r="43">
@@ -1427,16 +1427,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>156.81</v>
+        <v>150.95</v>
       </c>
       <c r="E43" t="n">
-        <v>2665.77</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>3038.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1451,16 +1451,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="D44" t="n">
-        <v>28.2</v>
+        <v>29.1</v>
       </c>
       <c r="E44" t="n">
-        <v>817.8</v>
+        <v>1949.7</v>
       </c>
       <c r="F44" t="n">
-        <v>1022.25</v>
+        <v>2437.46</v>
       </c>
     </row>
     <row r="45">
@@ -1475,16 +1475,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="D45" t="n">
-        <v>24.83</v>
+        <v>26.24</v>
       </c>
       <c r="E45" t="n">
-        <v>2259.53</v>
+        <v>944.64</v>
       </c>
       <c r="F45" t="n">
-        <v>2824.64</v>
+        <v>1180.8</v>
       </c>
     </row>
     <row r="46">
@@ -1499,16 +1499,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="D46" t="n">
-        <v>35.88</v>
+        <v>33.57</v>
       </c>
       <c r="E46" t="n">
-        <v>322.92</v>
+        <v>2316.33</v>
       </c>
       <c r="F46" t="n">
-        <v>397.17</v>
+        <v>2849.01</v>
       </c>
     </row>
     <row r="47">
@@ -1523,16 +1523,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D47" t="n">
-        <v>39.61</v>
+        <v>40.64</v>
       </c>
       <c r="E47" t="n">
-        <v>871.42</v>
+        <v>1219.2</v>
       </c>
       <c r="F47" t="n">
-        <v>1098.02</v>
+        <v>1536.3</v>
       </c>
     </row>
     <row r="48">
@@ -1547,16 +1547,16 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D48" t="n">
-        <v>232.34</v>
+        <v>228.66</v>
       </c>
       <c r="E48" t="n">
-        <v>929.36</v>
+        <v>3201.24</v>
       </c>
       <c r="F48" t="n">
-        <v>1096.64</v>
+        <v>3777.48</v>
       </c>
     </row>
     <row r="49">
@@ -1571,16 +1571,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D49" t="n">
-        <v>49.97</v>
+        <v>49.81</v>
       </c>
       <c r="E49" t="n">
-        <v>399.76</v>
+        <v>1743.35</v>
       </c>
       <c r="F49" t="n">
-        <v>495.68</v>
+        <v>2161.6</v>
       </c>
     </row>
     <row r="50">
@@ -1595,16 +1595,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D50" t="n">
-        <v>96.93000000000001</v>
+        <v>94.16</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>4237.2</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>5084.55</v>
       </c>
     </row>
     <row r="51">
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D51" t="n">
-        <v>45.15</v>
+        <v>44.06</v>
       </c>
       <c r="E51" t="n">
-        <v>225.75</v>
+        <v>1101.5</v>
       </c>
       <c r="F51" t="n">
-        <v>277.65</v>
+        <v>1354.75</v>
       </c>
     </row>
     <row r="52">
@@ -1643,16 +1643,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D52" t="n">
-        <v>133.7</v>
+        <v>140.36</v>
       </c>
       <c r="E52" t="n">
-        <v>3342.5</v>
+        <v>2526.48</v>
       </c>
       <c r="F52" t="n">
-        <v>3977.5</v>
+        <v>3006.54</v>
       </c>
     </row>
     <row r="53">
@@ -1667,16 +1667,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>436</v>
+        <v>10</v>
       </c>
       <c r="D53" t="n">
-        <v>163.73</v>
+        <v>163.81</v>
       </c>
       <c r="E53" t="n">
-        <v>71386.28</v>
+        <v>1638.1</v>
       </c>
       <c r="F53" t="n">
-        <v>86375.96000000001</v>
+        <v>1982.1</v>
       </c>
     </row>
     <row r="54">
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D54" t="n">
-        <v>70.86</v>
+        <v>69.81</v>
       </c>
       <c r="E54" t="n">
-        <v>1984.08</v>
+        <v>1116.96</v>
       </c>
       <c r="F54" t="n">
-        <v>2420.6</v>
+        <v>1362.72</v>
       </c>
     </row>
     <row r="55">
@@ -1715,16 +1715,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D55" t="n">
-        <v>60.31</v>
+        <v>60.78</v>
       </c>
       <c r="E55" t="n">
-        <v>723.72</v>
+        <v>2188.08</v>
       </c>
       <c r="F55" t="n">
-        <v>875.76</v>
+        <v>2647.44</v>
       </c>
     </row>
     <row r="56">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>21.53</v>
+        <v>22.05</v>
       </c>
       <c r="E56" t="n">
-        <v>193.77</v>
+        <v>110.25</v>
       </c>
       <c r="F56" t="n">
-        <v>246.06</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57">
@@ -1763,16 +1763,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D57" t="n">
-        <v>31.43</v>
+        <v>31.66</v>
       </c>
       <c r="E57" t="n">
-        <v>408.59</v>
+        <v>1044.78</v>
       </c>
       <c r="F57" t="n">
-        <v>506.61</v>
+        <v>1295.58</v>
       </c>
     </row>
     <row r="58">
@@ -1787,16 +1787,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="D58" t="n">
-        <v>672.15</v>
+        <v>671.3099999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>20164.5</v>
+        <v>53033.49</v>
       </c>
       <c r="F58" t="n">
-        <v>23794.2</v>
+        <v>62579.85</v>
       </c>
     </row>
     <row r="59">
@@ -1811,16 +1811,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D59" t="n">
-        <v>974.13</v>
+        <v>981.33</v>
       </c>
       <c r="E59" t="n">
-        <v>13637.82</v>
+        <v>74581.08</v>
       </c>
       <c r="F59" t="n">
-        <v>15819.86</v>
+        <v>86513.84</v>
       </c>
     </row>
     <row r="60">
@@ -1835,16 +1835,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="D60" t="n">
-        <v>544.4400000000001</v>
+        <v>523.72</v>
       </c>
       <c r="E60" t="n">
-        <v>45188.52</v>
+        <v>15187.88</v>
       </c>
       <c r="F60" t="n">
-        <v>52870.17</v>
+        <v>17769.75</v>
       </c>
     </row>
     <row r="61">
@@ -1859,16 +1859,16 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="D61" t="n">
-        <v>700.73</v>
+        <v>735.59</v>
       </c>
       <c r="E61" t="n">
-        <v>2102.19</v>
+        <v>59582.79</v>
       </c>
       <c r="F61" t="n">
-        <v>2459.55</v>
+        <v>69711.84</v>
       </c>
     </row>
     <row r="62">
@@ -1883,16 +1883,16 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D62" t="n">
-        <v>99.03</v>
+        <v>90.94</v>
       </c>
       <c r="E62" t="n">
-        <v>2970.9</v>
+        <v>2000.68</v>
       </c>
       <c r="F62" t="n">
-        <v>3565.2</v>
+        <v>2400.86</v>
       </c>
     </row>
     <row r="63">
@@ -1907,16 +1907,16 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D63" t="n">
-        <v>119.61</v>
+        <v>115.55</v>
       </c>
       <c r="E63" t="n">
-        <v>3468.69</v>
+        <v>3119.85</v>
       </c>
       <c r="F63" t="n">
-        <v>4127.86</v>
+        <v>3712.5</v>
       </c>
     </row>
     <row r="64">
@@ -1931,16 +1931,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="D64" t="n">
-        <v>396.89</v>
+        <v>410.2</v>
       </c>
       <c r="E64" t="n">
-        <v>22225.84</v>
+        <v>62350.4</v>
       </c>
       <c r="F64" t="n">
-        <v>23781.52</v>
+        <v>60479.28</v>
       </c>
     </row>
     <row r="65">
@@ -1955,16 +1955,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D65" t="n">
-        <v>218.82</v>
+        <v>211.36</v>
       </c>
       <c r="E65" t="n">
-        <v>1969.38</v>
+        <v>5495.36</v>
       </c>
       <c r="F65" t="n">
-        <v>1910.34</v>
+        <v>5825.04</v>
       </c>
     </row>
     <row r="66">
@@ -1979,16 +1979,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D66" t="n">
-        <v>252.02</v>
+        <v>266.98</v>
       </c>
       <c r="E66" t="n">
-        <v>11088.88</v>
+        <v>6140.54</v>
       </c>
       <c r="F66" t="n">
-        <v>11754.16</v>
+        <v>6509</v>
       </c>
     </row>
     <row r="67">
@@ -2003,16 +2003,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D67" t="n">
-        <v>145.75</v>
+        <v>143.1</v>
       </c>
       <c r="E67" t="n">
-        <v>4809.75</v>
+        <v>5151.6</v>
       </c>
       <c r="F67" t="n">
-        <v>5771.7</v>
+        <v>6181.92</v>
       </c>
     </row>
     <row r="68">
@@ -2027,16 +2027,16 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D68" t="n">
-        <v>49.85</v>
+        <v>53.68</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1449.36</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1782.81</v>
       </c>
     </row>
     <row r="69">
@@ -2051,16 +2051,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>49</v>
+        <v>493</v>
       </c>
       <c r="D69" t="n">
-        <v>24.05</v>
+        <v>22.3</v>
       </c>
       <c r="E69" t="n">
-        <v>1178.45</v>
+        <v>10993.9</v>
       </c>
       <c r="F69" t="n">
-        <v>1484.7</v>
+        <v>13853.3</v>
       </c>
     </row>
     <row r="70">
@@ -2075,16 +2075,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D70" t="n">
-        <v>25.89</v>
+        <v>28.16</v>
       </c>
       <c r="E70" t="n">
-        <v>155.34</v>
+        <v>760.3200000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>194.16</v>
+        <v>950.4</v>
       </c>
     </row>
     <row r="71">
@@ -2099,16 +2099,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D71" t="n">
-        <v>21.62</v>
+        <v>22</v>
       </c>
       <c r="E71" t="n">
-        <v>345.92</v>
+        <v>968</v>
       </c>
       <c r="F71" t="n">
-        <v>435.84</v>
+        <v>1219.68</v>
       </c>
     </row>
     <row r="72">
@@ -2123,16 +2123,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D72" t="n">
-        <v>30.06</v>
+        <v>28.15</v>
       </c>
       <c r="E72" t="n">
-        <v>180.36</v>
+        <v>337.8</v>
       </c>
       <c r="F72" t="n">
-        <v>223.62</v>
+        <v>418.92</v>
       </c>
     </row>
     <row r="73">
@@ -2147,16 +2147,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="D73" t="n">
-        <v>182.44</v>
+        <v>178.96</v>
       </c>
       <c r="E73" t="n">
-        <v>18608.88</v>
+        <v>4474</v>
       </c>
       <c r="F73" t="n">
-        <v>21213.96</v>
+        <v>5100.25</v>
       </c>
     </row>
     <row r="74">
@@ -2171,16 +2171,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D74" t="n">
-        <v>343.73</v>
+        <v>376.35</v>
       </c>
       <c r="E74" t="n">
-        <v>12374.28</v>
+        <v>12043.2</v>
       </c>
       <c r="F74" t="n">
-        <v>14230.44</v>
+        <v>13849.6</v>
       </c>
     </row>
     <row r="75">
@@ -2195,16 +2195,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D75" t="n">
-        <v>218.77</v>
+        <v>237.3</v>
       </c>
       <c r="E75" t="n">
-        <v>16407.75</v>
+        <v>16136.4</v>
       </c>
       <c r="F75" t="n">
-        <v>19032.75</v>
+        <v>18718.36</v>
       </c>
     </row>
     <row r="76">
@@ -2219,16 +2219,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D76" t="n">
-        <v>319.95</v>
+        <v>321.45</v>
       </c>
       <c r="E76" t="n">
-        <v>9918.450000000001</v>
+        <v>9643.5</v>
       </c>
       <c r="F76" t="n">
-        <v>11108.54</v>
+        <v>10800.6</v>
       </c>
     </row>
     <row r="77">
@@ -2243,16 +2243,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D77" t="n">
-        <v>64.06999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E77" t="n">
-        <v>2819.08</v>
+        <v>464.8</v>
       </c>
       <c r="F77" t="n">
-        <v>3382.72</v>
+        <v>557.76</v>
       </c>
     </row>
     <row r="78">
@@ -2267,16 +2267,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="D78" t="n">
-        <v>96.68000000000001</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="E78" t="n">
-        <v>8604.52</v>
+        <v>1496.85</v>
       </c>
       <c r="F78" t="n">
-        <v>10239.45</v>
+        <v>1781.25</v>
       </c>
     </row>
     <row r="79">
@@ -2291,16 +2291,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>383.64</v>
+        <v>386.7</v>
       </c>
       <c r="E79" t="n">
-        <v>77878.92</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>87225.03999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2315,16 +2315,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D80" t="n">
-        <v>1658.15</v>
+        <v>1678.24</v>
       </c>
       <c r="E80" t="n">
-        <v>58035.25</v>
+        <v>57060.16</v>
       </c>
       <c r="F80" t="n">
-        <v>63838.95</v>
+        <v>62766.04</v>
       </c>
     </row>
     <row r="81">
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>87.52</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -2363,16 +2363,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D82" t="n">
-        <v>61.45</v>
+        <v>58.13</v>
       </c>
       <c r="E82" t="n">
-        <v>1904.95</v>
+        <v>1046.34</v>
       </c>
       <c r="F82" t="n">
-        <v>2571.76</v>
+        <v>1412.64</v>
       </c>
     </row>
   </sheetData>
